--- a/Gravedigger2026/Assets/ConfigTables/Excel/关卡_子关卡表_Level_SubLevelConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/关卡_子关卡表_Level_SubLevelConfig.xlsx
@@ -615,7 +615,6 @@
           <t>升级与制造（PushMap_01）</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Opt_L01_S3_PushMap</t>
@@ -658,7 +657,6 @@
           <t>Spirit;20</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -780,7 +778,6 @@
           <t>Spirit;20</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -855,7 +852,6 @@
           <t>升级与制造（Dig_06）</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Opt_L03_S3_Defend</t>
@@ -940,7 +936,6 @@
           <t>Spirit;20</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/关卡_子关卡表_Level_SubLevelConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/关卡_子关卡表_Level_SubLevelConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,20 +439,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Tips图标2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>提示消息</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>标题文字</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>描述文字</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>奖励</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>解锁下一阶段选项</t>
         </is>
@@ -481,20 +491,30 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>路线图直显</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>路线图直显</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>ItemId;Count|…；可空；通关发放</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>OptId|OptId；须属 Stage+1；空=关卡胜利</t>
         </is>
@@ -523,20 +543,30 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>IconAssetId2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TipMessages</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Reward</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>UnlockNextOptionIds</t>
         </is>
@@ -563,22 +593,28 @@
           <t>Opt_L01_S1_Dig</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spirit;3|Wreck;-2|Warrior;2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>挖坟</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>挖坟（Dig_01）</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Spirit;20</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Opt_L01_S2_UpgradeManufacture</t>
         </is>
@@ -607,15 +643,21 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Opt_L01_S2_UpgradeManufacture</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>升级与制造</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>升级与制造（PushMap_01）</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Opt_L01_S3_PushMap</t>
         </is>
@@ -644,15 +686,21 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Opt_L01_S3_PushMap</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>推图战</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>推图战（PushMap_01）</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Spirit;20</t>
         </is>
@@ -679,22 +727,28 @@
           <t>Opt_L02_S1_Dig</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spirit;3|Wreck;-2|Warrior;2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>挖坟</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>挖坟（Dig_03）</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Spirit;20</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Opt_L02_S2_Defend</t>
         </is>
@@ -723,20 +777,26 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Opt_L02_S2_Defend</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>保卫战</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>保卫战（Defend_02）</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Spirit;20</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Opt_L02_S3_Dig</t>
         </is>
@@ -763,17 +823,23 @@
           <t>Opt_L02_S3_Dig</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spirit;3|Wreck;-2|Warrior;2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>挖坟</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>挖坟（Dig_04）</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Spirit;20</t>
         </is>
@@ -800,22 +866,28 @@
           <t>Opt_L03_S1_Dig</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spirit;3|Wreck;-2|Warrior;2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>挖坟</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>挖坟（Dig_05）</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Spirit;20</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Opt_L03_S2_UpgradeManufacture</t>
         </is>
@@ -844,15 +916,21 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Opt_L03_S2_UpgradeManufacture</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>升级与制造</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>升级与制造（Dig_06）</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Opt_L03_S3_Defend</t>
         </is>
@@ -881,20 +959,26 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Opt_L03_S3_Defend</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>保卫战</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>保卫战（Defend_03）</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Spirit;20</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Opt_L03_S4_Dig</t>
         </is>
@@ -921,17 +1005,23 @@
           <t>Opt_L03_S4_Dig</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spirit;3|Wreck;-2|Warrior;2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>挖坟</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>挖坟（Dig_07）</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Spirit;20</t>
         </is>
